--- a/Task 1.xlsx
+++ b/Task 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9a1e314b52a5af4/Desktop/DA Assignments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b9a1e314b52a5af4/Desktop/DA Assignments/Assignment 1 - ENTRI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DDC3BA3-C74C-41F9-941B-A74EBC28C7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{2DDC3BA3-C74C-41F9-941B-A74EBC28C7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11927A7D-0FC9-463C-BB45-545E03D49740}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E1703719-4FD6-49DB-8C53-ECA6BD52743E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="98">
   <si>
     <t>Product Name</t>
   </si>
@@ -510,6 +510,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -809,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38142FD7-E343-4707-BAC6-142CE7DF8962}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -1457,7 +1461,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>86</v>
       </c>
@@ -1477,7 +1481,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>39</v>
       </c>
@@ -1497,7 +1501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>89</v>
       </c>
@@ -1517,7 +1521,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1525,8 +1529,91 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
     </row>
+    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>1</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>2</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="12"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
+        <v>3</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="12"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>4</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="12"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="5">
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B43:I43"/>
+  </mergeCells>
+  <pageMargins left="1.0899999999999999" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="77" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
